--- a/4. Unregistered_Manual_Map.xlsx
+++ b/4. Unregistered_Manual_Map.xlsx
@@ -1,56 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Desktop\NCU Files to Upload to Gemini AI for Analysis\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17580"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17580" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>Player Name</t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFE0"/>
+        <bgColor rgb="00FFFFE0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -65,22 +57,82 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -346,19 +398,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col width="13" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Player Name</t>
+        </is>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Team</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/4. Unregistered_Manual_Map.xlsx
+++ b/4. Unregistered_Manual_Map.xlsx
@@ -3,20 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17580" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15060" yWindow="2400" windowWidth="21420" windowHeight="20490" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="162913" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,13 +30,22 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFE0"/>
+        <bgColor rgb="FFFFFFE0"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -57,9 +66,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -403,22 +413,130 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="26" bestFit="1" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Player Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tyler McGladdery</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Derriaghy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aidan O'Gorman</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CI 4th XI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sameer Mohammed</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Belfast 1st XI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Edward Lawther</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ards &amp; Donaghadee 3rd XI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Jacob Lawther</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ards &amp; Donaghadee 3rd XI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lokesh Gehani</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Downpatrick 4th XI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>James Cockcroft</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Donacloney Mill 3rd XI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Karin Gul</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Victoria 3rd XI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Oliver Bryans</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Derriaghy 3rd XI</t>
         </is>
       </c>
     </row>

--- a/4. Unregistered_Manual_Map.xlsx
+++ b/4. Unregistered_Manual_Map.xlsx
@@ -1,42 +1,105 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018606FE-3E4B-4C3C-8F85-38A156A0EEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="15060" yWindow="2400" windowWidth="21420" windowHeight="20490" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+  <si>
+    <t>Player Name</t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Tyler McGladdery</t>
+  </si>
+  <si>
+    <t>Aidan O'Gorman</t>
+  </si>
+  <si>
+    <t>CI 4th XI</t>
+  </si>
+  <si>
+    <t>Sameer Mohammed</t>
+  </si>
+  <si>
+    <t>Belfast 1st XI</t>
+  </si>
+  <si>
+    <t>Edward Lawther</t>
+  </si>
+  <si>
+    <t>Ards &amp; Donaghadee 3rd XI</t>
+  </si>
+  <si>
+    <t>Jacob Lawther</t>
+  </si>
+  <si>
+    <t>Lokesh Gehani</t>
+  </si>
+  <si>
+    <t>Downpatrick 4th XI</t>
+  </si>
+  <si>
+    <t>James Cockcroft</t>
+  </si>
+  <si>
+    <t>Donacloney Mill 3rd XI</t>
+  </si>
+  <si>
+    <t>Karin Gul</t>
+  </si>
+  <si>
+    <t>Victoria 3rd XI</t>
+  </si>
+  <si>
+    <t>Oliver Bryans</t>
+  </si>
+  <si>
+    <t>Derriaghy 3rd XI</t>
+  </si>
+  <si>
+    <t>Derriaghy 1st XI</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -45,12 +108,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFE0"/>
         <bgColor rgb="FFFFFFE0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFE0"/>
-        <bgColor rgb="00FFFFE0"/>
       </patternFill>
     </fill>
   </fills>
@@ -66,83 +123,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,136 +405,92 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="18" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="26" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Player Name</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Team</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Tyler McGladdery</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Derriaghy</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Aidan O'Gorman</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CI 4th XI</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Sameer Mohammed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Belfast 1st XI</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Edward Lawther</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Ards &amp; Donaghadee 3rd XI</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Jacob Lawther</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ards &amp; Donaghadee 3rd XI</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Lokesh Gehani</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Downpatrick 4th XI</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>James Cockcroft</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Donacloney Mill 3rd XI</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Karin Gul</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Victoria 3rd XI</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Oliver Bryans</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Derriaghy 3rd XI</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/4. Unregistered_Manual_Map.xlsx
+++ b/4. Unregistered_Manual_Map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018606FE-3E4B-4C3C-8F85-38A156A0EEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF93CE1-4DFB-4ACE-ACC7-7C9D2EB62EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19920" yWindow="600" windowWidth="18270" windowHeight="20250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="64">
   <si>
     <t>Player Name</t>
   </si>
@@ -34,49 +34,184 @@
     <t>Aidan O'Gorman</t>
   </si>
   <si>
-    <t>CI 4th XI</t>
-  </si>
-  <si>
-    <t>Sameer Mohammed</t>
-  </si>
-  <si>
-    <t>Belfast 1st XI</t>
-  </si>
-  <si>
     <t>Edward Lawther</t>
   </si>
   <si>
-    <t>Ards &amp; Donaghadee 3rd XI</t>
-  </si>
-  <si>
     <t>Jacob Lawther</t>
   </si>
   <si>
-    <t>Lokesh Gehani</t>
-  </si>
-  <si>
-    <t>Downpatrick 4th XI</t>
-  </si>
-  <si>
     <t>James Cockcroft</t>
   </si>
   <si>
-    <t>Donacloney Mill 3rd XI</t>
-  </si>
-  <si>
     <t>Karin Gul</t>
   </si>
   <si>
-    <t>Victoria 3rd XI</t>
-  </si>
-  <si>
     <t>Oliver Bryans</t>
   </si>
   <si>
-    <t>Derriaghy 3rd XI</t>
-  </si>
-  <si>
-    <t>Derriaghy 1st XI</t>
+    <t>Derriaghy</t>
+  </si>
+  <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>Belfast</t>
+  </si>
+  <si>
+    <t>Ards &amp; Donaghadee</t>
+  </si>
+  <si>
+    <t>Donacloney Mill</t>
+  </si>
+  <si>
+    <t>Victoria</t>
+  </si>
+  <si>
+    <t>Bradley Hodge</t>
+  </si>
+  <si>
+    <t>Shanmukh Kasibhatla</t>
+  </si>
+  <si>
+    <t>Maurya Shukla</t>
+  </si>
+  <si>
+    <t>Harry Knox</t>
+  </si>
+  <si>
+    <t>Tom Livingston</t>
+  </si>
+  <si>
+    <t>James Wootton</t>
+  </si>
+  <si>
+    <t>Archie McDowell</t>
+  </si>
+  <si>
+    <t>Alisha McKee</t>
+  </si>
+  <si>
+    <t>Isla McMullan</t>
+  </si>
+  <si>
+    <t>Ayla Boyd</t>
+  </si>
+  <si>
+    <t>Jack Mayne</t>
+  </si>
+  <si>
+    <t>Manjit Singh</t>
+  </si>
+  <si>
+    <t>Muckamore</t>
+  </si>
+  <si>
+    <t>Instonians</t>
+  </si>
+  <si>
+    <t>Cooke Collegians</t>
+  </si>
+  <si>
+    <t>Cliftonville Academy</t>
+  </si>
+  <si>
+    <t>CSNI</t>
+  </si>
+  <si>
+    <t>Drumaness Superkings</t>
+  </si>
+  <si>
+    <t>Dundrum</t>
+  </si>
+  <si>
+    <t>Lisburn</t>
+  </si>
+  <si>
+    <t>PSNI</t>
+  </si>
+  <si>
+    <t>Josh Hall</t>
+  </si>
+  <si>
+    <t>Danny Moby</t>
+  </si>
+  <si>
+    <t>Christy Rathesh</t>
+  </si>
+  <si>
+    <t>Joel McKean</t>
+  </si>
+  <si>
+    <t>Erin Smyth</t>
+  </si>
+  <si>
+    <t>Usman Siddiq</t>
+  </si>
+  <si>
+    <t>James Montgomery</t>
+  </si>
+  <si>
+    <t>Indie Allen</t>
+  </si>
+  <si>
+    <t>Vismithaa Pandiaraj</t>
+  </si>
+  <si>
+    <t>Lea Matthews</t>
+  </si>
+  <si>
+    <t>Molly Sawyer</t>
+  </si>
+  <si>
+    <t>Cora Perrin</t>
+  </si>
+  <si>
+    <t>Olivia Boyd</t>
+  </si>
+  <si>
+    <t>Ellie Hipson</t>
+  </si>
+  <si>
+    <t>Sarah Cowden</t>
+  </si>
+  <si>
+    <t>Rachel Murray</t>
+  </si>
+  <si>
+    <t>Lyla Cubitt</t>
+  </si>
+  <si>
+    <t>Ava Templeton</t>
+  </si>
+  <si>
+    <t>Rowan Foye</t>
+  </si>
+  <si>
+    <t>Usman Ahmed</t>
+  </si>
+  <si>
+    <t>Katie Harper</t>
+  </si>
+  <si>
+    <t>Dave Williams</t>
+  </si>
+  <si>
+    <t>Ali Quadri</t>
+  </si>
+  <si>
+    <t>Holywood 1881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCU Pathway XI </t>
+  </si>
+  <si>
+    <t>Ballymena</t>
+  </si>
+  <si>
+    <t>Templepatrick</t>
+  </si>
+  <si>
+    <t>Bangor</t>
   </si>
 </sst>
 </file>
@@ -406,10 +541,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -423,74 +558,338 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" t="s">
         <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>16</v>
       </c>
-      <c r="B10" t="s">
-        <v>17</v>
+      <c r="B38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
